--- a/data/trans_orig/barthel-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/barthel-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de dependencia funcional para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Puntuación media de la escala de dependencia funcional para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>95,58; 97,7</t>
+          <t>95,74; 97,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92,36; 95,62</t>
+          <t>92,23; 95,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93,27; 96,11</t>
+          <t>93,43; 96,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93,14; 95,51</t>
+          <t>93,06; 95,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,19; 96,37</t>
+          <t>94,0; 96,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,35; 92,34</t>
+          <t>89,34; 92,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,67; 93,74</t>
+          <t>90,44; 93,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,13; 90,6</t>
+          <t>88,03; 90,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94,92; 96,63</t>
+          <t>95,06; 96,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91,07; 93,39</t>
+          <t>91,15; 93,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92,07; 94,39</t>
+          <t>92,06; 94,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,18; 92,07</t>
+          <t>90,08; 92,01</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>96,83; 99,7</t>
+          <t>96,59; 99,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,21; 98,81</t>
+          <t>93,98; 98,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,44; 99,03</t>
+          <t>96,25; 98,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95,89; 97,98</t>
+          <t>96,02; 98,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,55; 99,03</t>
+          <t>90,32; 98,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,14; 97,62</t>
+          <t>89,92; 97,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,23; 97,84</t>
+          <t>95,32; 97,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>95,87; 99,34</t>
+          <t>95,88; 99,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95,1; 99,25</t>
+          <t>95,14; 99,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93,93; 98,11</t>
+          <t>94,01; 97,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96,38; 98,19</t>
+          <t>96,42; 98,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>96,47; 98,99</t>
+          <t>96,48; 98,94</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>98,04; 99,88</t>
+          <t>97,92; 99,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,08; 100,0</t>
+          <t>92,44; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,81; 99,48</t>
+          <t>93,52; 99,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98,19; 99,31</t>
+          <t>98,14; 99,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93,28; 99,38</t>
+          <t>94,18; 99,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,56; 98,52</t>
+          <t>82,89; 98,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,67; 99,55</t>
+          <t>88,92; 99,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>97,84; 99,13</t>
+          <t>97,81; 99,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97,06; 99,51</t>
+          <t>96,71; 99,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91,81; 98,69</t>
+          <t>91,6; 98,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93,45; 99,18</t>
+          <t>93,37; 99,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>98,32; 99,12</t>
+          <t>98,3; 99,14</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>96,28; 98,04</t>
+          <t>96,43; 98,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,51; 96,26</t>
+          <t>93,78; 96,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95,2; 96,95</t>
+          <t>95,21; 97,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95,54; 96,87</t>
+          <t>95,57; 96,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,41; 96,51</t>
+          <t>94,39; 96,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,12; 92,86</t>
+          <t>90,1; 92,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,15; 94,69</t>
+          <t>92,29; 94,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,96; 96,72</t>
+          <t>92,01; 96,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95,6; 96,98</t>
+          <t>95,54; 96,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92,07; 94,01</t>
+          <t>92,11; 94,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93,92; 95,47</t>
+          <t>93,9; 95,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,91; 96,78</t>
+          <t>93,89; 96,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/barthel-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/barthel-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94,36</t>
+          <t>94,49</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>89,44</t>
+          <t>89,36</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>95,74; 97,83</t>
+          <t>95,57; 97,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92,23; 95,73</t>
+          <t>92,49; 95,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93,43; 96,2</t>
+          <t>93,49; 96,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93,06; 95,36</t>
+          <t>93,15; 95,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,0; 96,27</t>
+          <t>94,03; 96,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,34; 92,46</t>
+          <t>89,42; 92,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,44; 93,69</t>
+          <t>90,38; 93,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,03; 90,53</t>
+          <t>88,04; 90,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>95,06; 96,63</t>
+          <t>94,98; 96,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91,15; 93,42</t>
+          <t>91,03; 93,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92,06; 94,28</t>
+          <t>92,15; 94,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,08; 92,01</t>
+          <t>90,18; 92,02</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97,22</t>
+          <t>97,36</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>97,89</t>
+          <t>96,09</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>97,64</t>
+          <t>96,76</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>96,59; 99,63</t>
+          <t>96,78; 99,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,98; 98,87</t>
+          <t>94,03; 98,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,25; 98,96</t>
+          <t>96,22; 98,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96,02; 98,01</t>
+          <t>96,04; 98,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,32; 98,93</t>
+          <t>89,78; 99,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,92; 97,94</t>
+          <t>89,31; 97,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,32; 97,9</t>
+          <t>95,19; 97,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>95,88; 99,33</t>
+          <t>94,96; 96,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95,14; 99,13</t>
+          <t>95,01; 99,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94,01; 97,95</t>
+          <t>93,66; 97,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96,42; 98,24</t>
+          <t>96,29; 98,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>96,48; 98,94</t>
+          <t>96,02; 97,35</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98,89</t>
+          <t>98,65</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>98,61</t>
+          <t>98,63</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,78</t>
+          <t>98,64</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97,92; 99,85</t>
+          <t>98,12; 99,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>92,44; 100,0</t>
+          <t>92,76; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>93,52; 99,47</t>
+          <t>93,22; 99,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98,14; 99,33</t>
+          <t>97,16; 99,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94,18; 99,48</t>
+          <t>94,13; 99,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,89; 98,33</t>
+          <t>83,91; 98,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,92; 99,5</t>
+          <t>88,46; 99,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>97,81; 99,11</t>
+          <t>97,89; 99,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>96,71; 99,5</t>
+          <t>96,89; 99,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91,6; 98,77</t>
+          <t>91,2; 98,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93,37; 99,28</t>
+          <t>93,36; 99,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>98,3; 99,14</t>
+          <t>97,87; 99,06</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96,3</t>
+          <t>96,41</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>93,85</t>
+          <t>92,31</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,8</t>
+          <t>94,13</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>96,43; 98,09</t>
+          <t>96,54; 98,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,78; 96,3</t>
+          <t>93,51; 96,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95,21; 97,04</t>
+          <t>95,21; 96,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95,57; 96,96</t>
+          <t>95,73; 96,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,39; 96,43</t>
+          <t>94,3; 96,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,1; 92,88</t>
+          <t>90,09; 92,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,29; 94,7</t>
+          <t>92,12; 94,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92,01; 96,66</t>
+          <t>91,43; 93,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95,54; 96,95</t>
+          <t>95,63; 96,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92,11; 94,15</t>
+          <t>92,11; 93,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93,9; 95,44</t>
+          <t>93,79; 95,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,89; 96,7</t>
+          <t>93,52; 94,65</t>
         </is>
       </c>
     </row>
